--- a/dados/gerencial/consolidado_gerencial_2022.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2022.xlsx
@@ -491,16 +491,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>939381.39</v>
+        <v>926243.84</v>
       </c>
       <c r="F4" t="n">
-        <v>646944.3199999999</v>
+        <v>640756.1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>44600</v>
@@ -519,16 +519,16 @@
         <v>79</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>377069.92</v>
+        <v>376809.15</v>
       </c>
       <c r="F5" t="n">
-        <v>244877.68</v>
+        <v>245745.62</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>44601</v>
+        <v>44607</v>
       </c>
     </row>
     <row r="6">
@@ -547,10 +547,10 @@
         <v>70</v>
       </c>
       <c r="E6" t="n">
-        <v>909424.29</v>
+        <v>913659.29</v>
       </c>
       <c r="F6" t="n">
-        <v>592594.3199999999</v>
+        <v>592412.61</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>44634</v>
@@ -569,16 +569,16 @@
         <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>332076</v>
+        <v>329498.1</v>
       </c>
       <c r="F7" t="n">
-        <v>203039.41</v>
+        <v>202344.05</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>44628</v>
+        <v>44630</v>
       </c>
     </row>
     <row r="8">
@@ -597,13 +597,13 @@
         <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>900539.01</v>
+        <v>890875.4399999999</v>
       </c>
       <c r="F8" t="n">
-        <v>613420.58</v>
+        <v>615277.59</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44663</v>
+        <v>44662</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>364067.48</v>
+        <v>361224.34</v>
       </c>
       <c r="F9" t="n">
-        <v>238774.81</v>
+        <v>234281.43</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>44662</v>
+        <v>44664</v>
       </c>
     </row>
     <row r="10">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D10" t="n">
         <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>972783.51</v>
+        <v>961242.2</v>
       </c>
       <c r="F10" t="n">
-        <v>630086.4399999999</v>
+        <v>633141.4399999999</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>44697</v>
+        <v>44693</v>
       </c>
     </row>
     <row r="11">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
         <v>24</v>
       </c>
       <c r="E11" t="n">
-        <v>369529.27</v>
+        <v>368814.48</v>
       </c>
       <c r="F11" t="n">
-        <v>236272.22</v>
+        <v>235483.91</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>44691</v>
+        <v>44690</v>
       </c>
     </row>
     <row r="12">
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D12" t="n">
         <v>108</v>
       </c>
       <c r="E12" t="n">
-        <v>1092125.89</v>
+        <v>1099589.25</v>
       </c>
       <c r="F12" t="n">
-        <v>731434.37</v>
+        <v>743715.64</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>44722</v>
@@ -722,13 +722,13 @@
         <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>434547.48</v>
+        <v>430653.52</v>
       </c>
       <c r="F13" t="n">
-        <v>271641.99</v>
+        <v>272729.67</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44721</v>
+        <v>44722</v>
       </c>
     </row>
     <row r="14">
@@ -747,13 +747,13 @@
         <v>95</v>
       </c>
       <c r="E14" t="n">
-        <v>1033354.74</v>
+        <v>1021604.63</v>
       </c>
       <c r="F14" t="n">
-        <v>707664.6899999999</v>
+        <v>697166.63</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44754</v>
+        <v>44757</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>43</v>
       </c>
       <c r="E15" t="n">
-        <v>533833.89</v>
+        <v>536212.01</v>
       </c>
       <c r="F15" t="n">
-        <v>329233.07</v>
+        <v>331781.25</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>44753</v>
+        <v>44754</v>
       </c>
     </row>
     <row r="16">
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D16" t="n">
         <v>103</v>
       </c>
       <c r="E16" t="n">
-        <v>1052693.27</v>
+        <v>1040044.33</v>
       </c>
       <c r="F16" t="n">
-        <v>732000.6899999999</v>
+        <v>732474.64</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>44782</v>
@@ -822,13 +822,13 @@
         <v>34</v>
       </c>
       <c r="E17" t="n">
-        <v>679226.72</v>
+        <v>671661.98</v>
       </c>
       <c r="F17" t="n">
-        <v>451565.14</v>
+        <v>457234.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>44785</v>
+        <v>44788</v>
       </c>
     </row>
     <row r="18">
@@ -847,13 +847,13 @@
         <v>101</v>
       </c>
       <c r="E18" t="n">
-        <v>1117106.63</v>
+        <v>1131743.93</v>
       </c>
       <c r="F18" t="n">
-        <v>804330.27</v>
+        <v>805428.15</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>44816</v>
+        <v>44812</v>
       </c>
     </row>
     <row r="19">
@@ -872,13 +872,13 @@
         <v>48</v>
       </c>
       <c r="E19" t="n">
-        <v>819565.61</v>
+        <v>819581.65</v>
       </c>
       <c r="F19" t="n">
-        <v>532174.71</v>
+        <v>532608.79</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>44819</v>
+        <v>44813</v>
       </c>
     </row>
     <row r="20">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D20" t="n">
         <v>139</v>
       </c>
       <c r="E20" t="n">
-        <v>1193398.19</v>
+        <v>1193497.82</v>
       </c>
       <c r="F20" t="n">
-        <v>811561.0699999999</v>
+        <v>825646.08</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44844</v>
+        <v>44847</v>
       </c>
     </row>
     <row r="21">
@@ -922,10 +922,10 @@
         <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>977355.13</v>
+        <v>964871.95</v>
       </c>
       <c r="F21" t="n">
-        <v>642581.41</v>
+        <v>640766.1</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>44844</v>
@@ -947,13 +947,13 @@
         <v>150</v>
       </c>
       <c r="E22" t="n">
-        <v>1508490.06</v>
+        <v>1507228.85</v>
       </c>
       <c r="F22" t="n">
-        <v>1031596.71</v>
+        <v>1046224.47</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>44873</v>
+        <v>44879</v>
       </c>
     </row>
     <row r="23">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D23" t="n">
         <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>1154508.02</v>
+        <v>1157202.6</v>
       </c>
       <c r="F23" t="n">
-        <v>764095.61</v>
+        <v>759262.02</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>44874</v>
+        <v>44879</v>
       </c>
     </row>
     <row r="24">
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D24" t="n">
         <v>167</v>
       </c>
       <c r="E24" t="n">
-        <v>1781869.53</v>
+        <v>1794497.53</v>
       </c>
       <c r="F24" t="n">
-        <v>1196105.05</v>
+        <v>1196904.01</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44909</v>
+        <v>44907</v>
       </c>
     </row>
     <row r="25">
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D25" t="n">
         <v>88</v>
       </c>
       <c r="E25" t="n">
-        <v>1323534.63</v>
+        <v>1329032.89</v>
       </c>
       <c r="F25" t="n">
-        <v>852309.3100000001</v>
+        <v>852452.4399999999</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>44910</v>
+        <v>44908</v>
       </c>
     </row>
     <row r="26">
@@ -1047,13 +1047,13 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>15861.01</v>
+        <v>15924.95</v>
       </c>
       <c r="F26" t="n">
-        <v>8469.07</v>
+        <v>8644.860000000001</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>44907</v>
+        <v>44908</v>
       </c>
     </row>
     <row r="27">
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D27" t="n">
         <v>166</v>
       </c>
       <c r="E27" t="n">
-        <v>1793076.78</v>
+        <v>1788558.58</v>
       </c>
       <c r="F27" t="n">
-        <v>1245631.1</v>
+        <v>1257844.82</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>44942</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="28">
@@ -1097,13 +1097,13 @@
         <v>74</v>
       </c>
       <c r="E28" t="n">
-        <v>1280572.93</v>
+        <v>1279129.17</v>
       </c>
       <c r="F28" t="n">
-        <v>854965.24</v>
+        <v>844854.72</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>44936</v>
+        <v>44935</v>
       </c>
     </row>
     <row r="29">
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>30311.66</v>
+        <v>31208.35</v>
       </c>
       <c r="F29" t="n">
-        <v>18934.8</v>
+        <v>19687.96</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>44935</v>
+        <v>44937</v>
       </c>
     </row>
     <row r="30">
@@ -1141,10 +1141,10 @@
         <v>1902</v>
       </c>
       <c r="E30" t="n">
-        <v>22986303.04</v>
+        <v>22940610.83</v>
       </c>
       <c r="F30" t="n">
-        <v>15392304.08</v>
+        <v>15424869.15</v>
       </c>
     </row>
   </sheetData>
